--- a/data/excel/all.xlsx
+++ b/data/excel/all.xlsx
@@ -77,7 +77,8 @@
 不填就默认cs</t>
   </si>
   <si>
-    <t>把不同的sheet里面的数据合并到一个文件中</t>
+    <t>导出文件名,不填就用Sheet名作为导出文件名
+也可以把不同的sheet里面的数据合并到一个文件中</t>
   </si>
   <si>
     <t>导出到代码里的注释</t>
@@ -1320,7 +1321,7 @@
     <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="18.75" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="24.5" customWidth="1"/>
     <col min="8" max="8" width="27.625" customWidth="1"/>
     <col min="9" max="9" width="23.75" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
@@ -1357,7 +1358,7 @@
       </c>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" ht="54" spans="1:9">
+    <row r="2" ht="54" spans="1:10">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1386,7 +1387,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1400,7 +1401,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1417,7 +1418,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -1434,7 +1435,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:8">
+    <row r="6" customFormat="1" spans="1:10">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1466,7 +1467,7 @@
       </c>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>38</v>
       </c>
